--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,29 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{"3": "Pangui", "4": "2026", "5": "1A"}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-02-04 00:08:23</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,75 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>2026-02-04 00:08:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Adolfo Farfal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{"3": "Pangui", "4": "2026", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-02-04 00:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Claudio Beltrán</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2025", "5": "3A"}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-02-04 00:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{"Presidente":"Gabriel","Tesorero":"Felipe","Secretario":"Paulina","Inversión":"50000"}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{"4": "2026", "5": "1A"}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-02-04 00:10:54</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>updated_at</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -477,6 +482,7 @@
           <t>2026-02-04 00:08:23</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -500,6 +506,7 @@
           <t>2026-02-04 00:10:05</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -523,6 +530,7 @@
           <t>2026-02-04 00:10:17</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -544,6 +552,31 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>2026-02-04 00:10:54</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{"Presidente": "Miguel", "Tesorero": "Andres", "Secretario": "Manuel", "Inversi\u00f3n": 100000}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"4": "2026", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-02-07T11:23:51.394515</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,121 +462,3049 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Presidente":"Gabriel","Tesorero":"Felipe","Secretario":"Paulina","Inversión":"50000"}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"3": "Pangui", "4": "2026", "5": "1A"}</t>
+          <t>{"4": "2026", "5": "1A"}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-04 00:08:23</t>
+          <t>2026-02-04 00:10:54</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adolfo Farfal</t>
+          <t>{"Presidente": "Miguel", "Tesorero": "Andres", "Secretario": "Manuel", "Inversi\u00f3n": 100000}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"3": "Pangui", "4": "2026", "5": "2A"}</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-02-04 00:10:05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>{"4": "2026", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-02-07T11:23:51.394515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Claudio Beltrán</t>
+          <t>Miguel Godoy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2025", "5": "3A"}</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-02-04 00:10:17</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-02-12T17:55:36.103828</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"Presidente":"Gabriel","Tesorero":"Felipe","Secretario":"Paulina","Inversión":"50000"}</t>
+          <t>Jaime Jaimes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"4": "2026", "5": "1A"}</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-02-04 00:10:54</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-12T17:55:36.103828</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"Presidente": "Miguel", "Tesorero": "Andres", "Secretario": "Manuel", "Inversi\u00f3n": 100000}</t>
+          <t>Atila el Huno</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"4": "2026", "5": "2A"}</t>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-07T11:23:51.394515</t>
+          <t>2026-02-12T17:55:36.103828</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:29.011630</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jaime Jaimes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:29.011630</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Atila el Huno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:29.011630</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:46.260527</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jaime Jaimes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:46.260527</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Atila el Huno</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:46.260527</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:59.834251</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jaime Jaimes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:59.834251</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atila el Huno</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:01:59.834251</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:06.562947</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jaime Jaimes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:06.562947</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atila el Huno</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:06.562947</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Miguel Godoy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:13.015581</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jaime Jaimes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:13.015581</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atila el Huno</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:02:13.015581</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.122299</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>25</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>27</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>28</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>29</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.123300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>31</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>33</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>34</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>37</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>38</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>39</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>41</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>42</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.124301</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>43</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>44</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>45</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>47</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.126808</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>49</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.126808</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>50</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.126808</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>51</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.126808</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>52</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127311</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>53</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127311</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>54</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>55</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>56</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>57</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>58</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>59</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>60</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>61</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.127823</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>62</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>63</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>64</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>65</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>66</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>67</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>68</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>69</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>70</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>71</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>72</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>73</v>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>74</v>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.128827</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>75</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.130329</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>76</v>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.130329</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>77</v>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.130329</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>78</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.130329</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>79</v>
+      </c>
+      <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>80</v>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>81</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>82</v>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>83</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>84</v>
+      </c>
+      <c r="B82" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>85</v>
+      </c>
+      <c r="B83" t="n">
+        <v>4</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>86</v>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>87</v>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.131332</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>88</v>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>93</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>94</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>95</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.132332</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>96</v>
+      </c>
+      <c r="B94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>97</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>98</v>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>99</v>
+      </c>
+      <c r="B97" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>100</v>
+      </c>
+      <c r="B98" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>101</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>102</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>103</v>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>104</v>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.133332</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>105</v>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 25.6, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>106</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>107</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>108</v>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>109</v>
+      </c>
+      <c r="B107" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>110</v>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>111</v>
+      </c>
+      <c r="B109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>112</v>
+      </c>
+      <c r="B110" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.134332</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>113</v>
+      </c>
+      <c r="B111" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.135332</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>114</v>
+      </c>
+      <c r="B112" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.135332</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>115</v>
+      </c>
+      <c r="B113" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.135332</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>116</v>
+      </c>
+      <c r="B114" t="n">
+        <v>4</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.135332</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>117</v>
+      </c>
+      <c r="B115" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.135332</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>118</v>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>119</v>
+      </c>
+      <c r="B117" t="n">
+        <v>4</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120</v>
+      </c>
+      <c r="B118" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121</v>
+      </c>
+      <c r="B119" t="n">
+        <v>4</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>122</v>
+      </c>
+      <c r="B120" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>123</v>
+      </c>
+      <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.136332</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>124</v>
+      </c>
+      <c r="B122" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137331</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>125</v>
+      </c>
+      <c r="B123" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137331</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>126</v>
+      </c>
+      <c r="B124" t="n">
+        <v>4</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137331</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127</v>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137331</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128</v>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137834</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129</v>
+      </c>
+      <c r="B127" t="n">
+        <v>4</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137834</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>130</v>
+      </c>
+      <c r="B128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{"5": "2\u00b0 medio D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.137834</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,3047 +462,2567 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"Presidente":"Gabriel","Tesorero":"Felipe","Secretario":"Paulina","Inversión":"50000"}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"4": "2026", "5": "1A"}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-02-04 00:10:54</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>{"5": "2\u00b0 medio A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:51:15.122299</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"Presidente": "Miguel", "Tesorero": "Andres", "Secretario": "Manuel", "Inversi\u00f3n": 100000}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"4": "2026", "5": "2A"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-07T11:23:51.394515</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-12T17:55:36.103828</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-12T17:55:36.103828</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-12T17:55:36.103828</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:29.011630</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:29.011630</t>
+          <t>2026-02-13T11:51:15.123300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:29.011630</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:46.260527</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:46.260527</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:46.260527</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:59.834251</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:59.834251</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-12T18:01:59.834251</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:06.562947</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:06.562947</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:06.562947</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miguel Godoy</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "1A", "6": "18720297-3"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:13.015581</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jaime Jaimes</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"3": "Panguipulli", "4": "2026", "5": "1A", "6": "12354-4"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:13.015581</t>
+          <t>2026-02-13T11:51:15.124301</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atila el Huno</t>
+          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"3": "Pullinque", "4": "2026", "5": "2A", "6": "2026-01-11 00:00:00"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-12T18:02:13.015581</t>
+          <t>2026-02-13T11:51:15.125804</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.122299</t>
+          <t>2026-02-13T11:51:15.125804</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.125804</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.125804</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.125804</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.126808</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.126808</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-02-13T11:51:15.126808</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.126808</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127311</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127311</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.127823</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B43" t="n">
         <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B44" t="n">
         <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127311</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B51" t="n">
         <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127311</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B52" t="n">
         <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.128827</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B53" t="n">
         <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.130329</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B54" t="n">
         <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.130329</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.130329</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.130329</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B58" t="n">
         <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B61" t="n">
         <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B62" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B64" t="n">
         <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.131332</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B66" t="n">
         <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B67" t="n">
         <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B71" t="n">
         <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B72" t="n">
         <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-02-13T11:51:15.132332</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B74" t="n">
         <v>4</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B76" t="n">
         <v>4</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B78" t="n">
         <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B81" t="n">
         <v>4</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.133332</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B83" t="n">
         <v>4</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 25.6, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B86" t="n">
         <v>4</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B87" t="n">
         <v>4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B88" t="n">
         <v>4</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="B90" t="n">
         <v>4</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.134332</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="B91" t="n">
         <v>4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.135332</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B92" t="n">
         <v>4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.135332</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-02-13T11:51:15.135332</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B94" t="n">
         <v>4</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.135332</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.135332</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="B96" t="n">
         <v>4</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B97" t="n">
         <v>4</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B98" t="n">
         <v>4</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B99" t="n">
         <v>4</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B100" t="n">
         <v>4</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B101" t="n">
         <v>4</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.136332</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B102" t="n">
         <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-02-13T11:51:15.137331</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B103" t="n">
         <v>4</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 25.6, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-02-13T11:51:15.137331</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B104" t="n">
         <v>4</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-02-13T11:51:15.137331</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-02-13T11:51:15.137331</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B106" t="n">
         <v>4</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-02-13T11:51:15.137834</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B107" t="n">
         <v>4</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-02-13T11:51:15.137834</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2\u00b0 medio D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.134332</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>111</v>
-      </c>
-      <c r="B109" t="n">
-        <v>4</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.134332</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>112</v>
-      </c>
-      <c r="B110" t="n">
-        <v>4</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.134332</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>113</v>
-      </c>
-      <c r="B111" t="n">
-        <v>4</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.135332</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>114</v>
-      </c>
-      <c r="B112" t="n">
-        <v>4</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.135332</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>115</v>
-      </c>
-      <c r="B113" t="n">
-        <v>4</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.135332</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>116</v>
-      </c>
-      <c r="B114" t="n">
-        <v>4</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.135332</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>117</v>
-      </c>
-      <c r="B115" t="n">
-        <v>4</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.135332</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>118</v>
-      </c>
-      <c r="B116" t="n">
-        <v>4</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>119</v>
-      </c>
-      <c r="B117" t="n">
-        <v>4</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>120</v>
-      </c>
-      <c r="B118" t="n">
-        <v>4</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>121</v>
-      </c>
-      <c r="B119" t="n">
-        <v>4</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>122</v>
-      </c>
-      <c r="B120" t="n">
-        <v>4</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>123</v>
-      </c>
-      <c r="B121" t="n">
-        <v>4</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.136332</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>124</v>
-      </c>
-      <c r="B122" t="n">
-        <v>4</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137331</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>125</v>
-      </c>
-      <c r="B123" t="n">
-        <v>4</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137331</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>126</v>
-      </c>
-      <c r="B124" t="n">
-        <v>4</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137331</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>127</v>
-      </c>
-      <c r="B125" t="n">
-        <v>4</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137331</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>128</v>
-      </c>
-      <c r="B126" t="n">
-        <v>4</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137834</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>129</v>
-      </c>
-      <c r="B127" t="n">
-        <v>4</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-02-13T11:51:15.137834</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>130</v>
-      </c>
-      <c r="B128" t="n">
-        <v>4</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
         <is>
           <t>2026-02-13T11:51:15.137834</t>
         </is>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,799 +462,799 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.122299</t>
+          <t>2026-03-03T18:33:27.594481</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.594577</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.594670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.594740</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.594820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.594929</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.123300</t>
+          <t>2026-03-03T18:33:27.595001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595257</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595465</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595537</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595617</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595687</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595753</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595820</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595886</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.595953</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B18" t="n">
         <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.596019</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.596093</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.124301</t>
+          <t>2026-03-03T18:33:27.596162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-03-03T18:33:27.596227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-03-03T18:33:27.596293</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-03-03T18:33:27.596360</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-03-03T18:33:27.596425</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.125804</t>
+          <t>2026-03-03T18:33:27.596491</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-03-03T18:33:27.596557</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-03-03T18:33:27.596633</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-03-03T18:33:27.596701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.126808</t>
+          <t>2026-03-03T18:33:27.596780</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127311</t>
+          <t>2026-03-03T18:33:27.596877</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127311</t>
+          <t>2026-03-03T18:33:27.596984</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597098</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597209</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597321</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
@@ -1266,19 +1266,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597424</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
@@ -1290,355 +1290,355 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597524</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597662</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597797</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.127823</t>
+          <t>2026-03-03T18:33:27.597910</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.597980</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598059</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598127</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B43" t="n">
         <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598203</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B44" t="n">
         <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598271</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598338</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598405</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598471</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
+          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598538</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598611</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598679</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
         <v>4</v>
@@ -1650,331 +1650,331 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598747</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B52" t="n">
         <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.128827</t>
+          <t>2026-03-03T18:33:27.598806</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B53" t="n">
         <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-03-03T18:33:27.598866</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B54" t="n">
         <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-03-03T18:33:27.598926</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-03-03T18:33:27.598987</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.130329</t>
+          <t>2026-03-03T18:33:27.599050</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599113</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B58" t="n">
         <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599176</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599239</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599302</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B61" t="n">
         <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599366</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B62" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599429</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599492</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B64" t="n">
         <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599554</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B65" t="n">
         <v>4</v>
@@ -1986,427 +1986,427 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.131332</t>
+          <t>2026-03-03T18:33:27.599662</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B66" t="n">
         <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.599731</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B67" t="n">
         <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.599803</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.599864</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.599924</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.599983</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B71" t="n">
         <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.600051</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B72" t="n">
         <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.600111</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.132332</t>
+          <t>2026-03-03T18:33:27.600169</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B74" t="n">
         <v>4</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600229</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600288</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B76" t="n">
         <v>4</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600348</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600408</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="B78" t="n">
         <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600468</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600528</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600593</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="B81" t="n">
         <v>4</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600667</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.133332</t>
+          <t>2026-03-03T18:33:27.600735</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B83" t="n">
         <v>4</v>
@@ -2418,19 +2418,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.600798</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B84" t="n">
         <v>4</v>
@@ -2442,19 +2442,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.600860</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="B85" t="n">
         <v>4</v>
@@ -2466,19 +2466,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.600921</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B86" t="n">
         <v>4</v>
@@ -2490,19 +2490,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.600982</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B87" t="n">
         <v>4</v>
@@ -2514,19 +2514,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.601043</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B88" t="n">
         <v>4</v>
@@ -2538,19 +2538,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.601103</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B89" t="n">
         <v>4</v>
@@ -2562,19 +2562,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.601164</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B90" t="n">
         <v>4</v>
@@ -2586,19 +2586,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.134332</t>
+          <t>2026-03-03T18:33:27.601224</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B91" t="n">
         <v>4</v>
@@ -2610,19 +2610,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.135332</t>
+          <t>2026-03-03T18:33:27.601284</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B92" t="n">
         <v>4</v>
@@ -2634,19 +2634,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.135332</t>
+          <t>2026-03-03T18:33:27.601345</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
@@ -2658,19 +2658,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.135332</t>
+          <t>2026-03-03T18:33:27.601405</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B94" t="n">
         <v>4</v>
@@ -2682,19 +2682,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.135332</t>
+          <t>2026-03-03T18:33:27.601469</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
@@ -2706,19 +2706,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.135332</t>
+          <t>2026-03-03T18:33:27.601531</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B96" t="n">
         <v>4</v>
@@ -2730,19 +2730,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.601601</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B97" t="n">
         <v>4</v>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.601686</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B98" t="n">
         <v>4</v>
@@ -2778,19 +2778,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.601753</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B99" t="n">
         <v>4</v>
@@ -2802,19 +2802,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.601818</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B100" t="n">
         <v>4</v>
@@ -2826,19 +2826,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.601884</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="B101" t="n">
         <v>4</v>
@@ -2850,19 +2850,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.136332</t>
+          <t>2026-03-03T18:33:27.602216</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B102" t="n">
         <v>4</v>
@@ -2874,19 +2874,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137331</t>
+          <t>2026-03-03T18:33:27.602283</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B103" t="n">
         <v>4</v>
@@ -2898,19 +2898,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137331</t>
+          <t>2026-03-03T18:33:27.602349</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B104" t="n">
         <v>4</v>
@@ -2922,19 +2922,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137331</t>
+          <t>2026-03-03T18:33:27.602415</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B105" t="n">
         <v>4</v>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137331</t>
+          <t>2026-03-03T18:33:27.602485</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B106" t="n">
         <v>4</v>
@@ -2970,19 +2970,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137834</t>
+          <t>2026-03-03T18:33:27.602552</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B107" t="n">
         <v>4</v>
@@ -2994,19 +2994,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137834</t>
+          <t>2026-03-03T18:33:27.602635</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B108" t="n">
         <v>4</v>
@@ -3018,13 +3018,3853 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{"5": "2\u00b0 medio D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-13T11:51:15.137834</t>
+          <t>2026-03-03T18:33:27.602734</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560304</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 2.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560381</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 15.0, "C": 0.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560446</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 3.0, "C": 19.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560509</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>5</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>{"A": 18.0, "B": 4.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560572</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560647</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>5</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 6.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560713</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 0.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560777</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 6.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560834</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 6.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560891</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>5</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 0.0, "C": 10.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.560948</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>5</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>{"A": 18.0, "B": 1.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561005</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>5</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 11.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561063</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 15.0, "C": 5.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561120</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>5</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 3.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561178</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>5</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 15.0, "C": 4.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561237</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>5</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>{"A": 12.0, "B": 2.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561294</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 1.0, "C": 15.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561352</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 0.0, "C": 0.0, "D": 13.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561409</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 16.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561467</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561524</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>5</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 13.0, "C": 3.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561581</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>5</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 5.0, "C": 3.0, "D": 16.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561664</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 10.0, "C": 7.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561729</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>5</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 9.0, "C": 3.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561793</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 4.0, "C": 11.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561856</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>5</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 0.0, "C": 20.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561919</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>5</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 11.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.561982</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>5</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562044</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>5</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 8.0, "C": 5.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562107</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>5</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 4.0, "C": 4.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562171</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 13.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562235</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 1.0, "C": 5.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562298</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>5</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 2.0, "C": 2.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562362</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>5</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562427</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>5</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 14.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562490</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>5</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562553</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 4.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562626</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 7.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562691</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>5</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 0.0, "C": 7.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B"}</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562749</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 8.0, "C": 3.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562807</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 5.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562868</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 15.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562932</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.562995</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>{"A": 23.0, "B": 2.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563057</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 1.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563120</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 5.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563183</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 5.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563245</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 5.0, "C": 4.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563308</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>5</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 3.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563372</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>5</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 0.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563434</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>{"A": 22.0, "B": 2.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563497</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 18.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563560</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 15.0, "C": 4.0, "D": 6.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563695</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563762</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>5</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 14.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563824</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>5</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 2.0, "C": 9.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563887</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.563950</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 0.0, "C": 3.0, "D": 7.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564013</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 22.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564076</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>5</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 1.0, "C": 13.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564140</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 17.0, "C": 2.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564204</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 3.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564326</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 9.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564405</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564468</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>{"A": 10.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564533</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 16.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564599</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 15.0, "C": 0.0, "D": 10.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564683</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>5</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 6.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564748</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 6.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564805</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>5</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 7.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564862</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>5</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 11.0, "C": 3.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564919</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 3.0, "C": 13.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.564976</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 4.0, "C": 1.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565032</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565089</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 19.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565145</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 7.0, "C": 18.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565201</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 4.0, "C": 22.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565260</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565317</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 0.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D"}</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565374</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 11.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565432</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>5</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 5.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565489</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>5</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 16.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565546</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>5</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 6.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565618</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>5</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 2.0, "C": 4.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565692</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>5</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565755</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>5</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 5.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565819</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>5</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 0.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565882</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>5</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 2.0, "C": 4.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.565946</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>5</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 1.0, "C": 9.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566010</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>5</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566073</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>5</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 0.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566136</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>5</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 14.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566199</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>5</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 13.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566262</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>5</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 0.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566326</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>5</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566388</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>5</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>{"A": 14.0, "B": 3.0, "C": 3.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566452</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 1.0, "C": 14.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566514</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>5</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 0.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566577</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>5</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 19.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566668</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>5</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 15.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566727</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>5</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 18.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566783</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>5</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 1.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566841</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>5</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 12.0, "C": 6.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566899</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>5</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.566956</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>5</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 3.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567013</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>5</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 18.0, "D": 2.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567070</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 13.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567127</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>5</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 1.0, "C": 5.0, "D": 18.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567184</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>5</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567240</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>5</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567298</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>5</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 15.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567355</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>5</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 4.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567413</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>5</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 2.0, "C": 1.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567471</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>5</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 2.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567528</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>5</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 20.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567607</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>5</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 17.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567683</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567746</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>5</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 3.0, "C": 0.0, "D": 5.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567808</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>5</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 19.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A"}</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567865</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>5</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 14.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567922</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>5</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>{"A": 26.0, "B": 3.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.567979</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>5</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568036</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>5</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 5.0, "C": 24.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568093</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>5</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>{"A": 29.0, "B": 1.0, "C": 2.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568152</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>5</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 2.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568209</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>5</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>{"A": 24.0, "B": 9.0, "C": 0.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568266</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>5</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 2.0, "C": 8.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568323</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>5</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 3.0, "C": 12.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568380</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>5</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 4.0, "C": 11.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568438</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>5</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 2.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568496</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>5</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>{"A": 28.0, "B": 2.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568554</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>5</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 16.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568639</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>5</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 20.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568706</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>5</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 3.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568770</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>5</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 17.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568828</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>5</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>{"A": 17.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568885</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 3.0, "C": 22.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.568942</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>5</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 3.0, "C": 3.0, "D": 12.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569000</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>5</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 23.0, "C": 6.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569058</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>5</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 4.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569115</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>5</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 21.0, "C": 3.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569172</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>5</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 3.0, "C": 1.0, "D": 28.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569229</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>5</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 18.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569286</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>5</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569343</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>5</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 11.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569407</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>5</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 2.0, "C": 21.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569471</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>5</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 16.0, "C": 2.0, "D": 13.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569533</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>5</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569605</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>5</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 8.0, "C": 13.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569672</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>5</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 7.0, "C": 9.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569736</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>5</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 24.0, "C": 2.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569802</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>5</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 3.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569867</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>5</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 3.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569932</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>5</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.569997</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>5</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.570063</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>5</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 4.0, "C": 22.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.570128</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 12.0, "C": 15.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.570193</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>5</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 10.0, "C": 1.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.570259</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>5</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C"}</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:33:28.570326</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,6414 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.597755</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.597834</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.597898</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.597961</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598028</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598092</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598154</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598215</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598277</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598338</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598467</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598530</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598591</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598653</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598714</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598775</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598835</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598896</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.598956</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599016</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599093</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599160</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599226</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599293</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599361</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599421</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599482</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599542</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599603</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599663</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599723</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"5": "2C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599785</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599847</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599909</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.599970</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600033</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600094</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600155</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600215</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600275</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600336</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600398</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600458</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600520</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600580</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600641</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600701</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600762</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600823</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600884</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.600945</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601006</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601075</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601143</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601206</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"5": "2A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601266</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601327</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601388</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601448</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601509</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601569</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601629</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601690</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601750</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601811</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601871</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601932</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.601993</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602060</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602129</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602194</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602254</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602315</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602375</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602436</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602498</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602565</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602662</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602743</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{"5": "2B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602812</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>4</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 25.6, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23260659-2", "7": "BENJAM\u00cdN ALONSO RUIZ SEP\u00daLVEDA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602880</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23147648-2", "7": "CONSTANZA MAGDALENA HERN\u00c1NDEZ PARADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.602947</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23123655-4", "7": "DANIEL ALEJANDRO ARANEDA INFANTE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603014</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "22623080-7", "7": "ELISA N\u00d6EL CASTILLO PASTENE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603091</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23222221-2", "7": "FABI\u00c1N ESTEBAN ALIU LINCOCHEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603159</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23223725-2", "7": "FELIPE EUGENIO CARIP\u00c1N LLAPELEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603225</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23209728-0", "7": "FELIPE IGNACIO LARA CAMPOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603286</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23075733-K", "7": "FRANKO JUSTINO CARRASCO BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603348</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "22600443-2", "7": "GUSTAVO JES\u00daS GUAJARDO LLONCO\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603409</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23206392-0", "7": "HORTENCIA ALEJANDRA ANCAMILLA MILLAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603470</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23071865-2", "7": "ISMAEL LUCIANO CALFI\u00d1IR HUENU\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603532</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23284555-4", "7": "JAVIER IGNACIO OLAVARR\u00cdA CUEVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603593</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "24309656-1", "7": "JEANEN PE\u00d1A", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603656</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23210749-9", "7": "LILIANA IGNACIA MADARIAGA ANCAMILLA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603723</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23201622-1", "7": "LUCAS IGNACIO BENJAM\u00cdN ALA\u00d1ANCO BRICE\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603804</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23169236-3", "7": "MADELEINE INES P\u00c9REZ ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.603900</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "22596306-1", "7": "MARTINA ANA\u00cdS G\u00d3MEZ PACHECO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604002</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23221210-1", "7": "MARTINA PASCAL LEFIQUEO ANTILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604096</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23207278-4", "7": "MAT\u00cdAS FRANCHESCO \u00c1LAMOS LLEUFUMAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604168</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23020358-K", "7": "MOIS\u00c9S ALONSO DUR\u00c1N BERROCAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604237</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "22833690-4", "7": "NAYELI MANQUELIPE BURGOS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604305</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23177773-3", "7": "NEYBER BENJAM\u00cdN CHAND\u00cdA MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604367</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23061855-0", "7": "RODRIGO FERNANDO CH\u00c1VEZ MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604429</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23229067-6", "7": "SIGRID NAYARETH BEL\u00c9N BURGOS ESPINOZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604503</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23296820-6", "7": "TERECITA DEL NI\u00d1O JES\u00daS CARES MONS\u00c1LVEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604601</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{"5": "2D", "6": "23077160-K", "7": "YOHAN RICARDO PROVOTH ARAVENA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:23.604685</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260577</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 2.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260659</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 15.0, "C": 0.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260728</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 3.0, "C": 19.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260795</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>5</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>{"A": 18.0, "B": 4.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260864</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260930</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>5</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 6.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.260995</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 0.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261083</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 6.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261151</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 6.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261216</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>5</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 0.0, "C": 10.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261282</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>5</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>{"A": 18.0, "B": 1.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261348</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>5</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 11.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261413</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 15.0, "C": 5.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261478</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>5</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 3.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261544</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>5</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 15.0, "C": 4.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261609</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>5</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>{"A": 12.0, "B": 2.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261674</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 1.0, "C": 15.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261739</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 0.0, "C": 0.0, "D": 13.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261804</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 16.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261869</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261934</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>5</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 13.0, "C": 3.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.261999</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>5</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 5.0, "C": 3.0, "D": 16.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262071</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 10.0, "C": 7.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262136</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>5</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 9.0, "C": 3.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262201</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 4.0, "C": 11.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262266</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>5</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 0.0, "C": 20.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262330</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>5</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 11.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262396</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>5</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262462</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>5</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 8.0, "C": 5.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262527</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>5</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 4.0, "C": 4.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262592</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 13.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262657</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 1.0, "C": 5.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262721</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>5</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 2.0, "C": 2.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262786</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>5</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262850</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>5</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 14.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262915</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>5</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.262980</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 4.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263052</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 7.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263118</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>5</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 0.0, "C": 7.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263183</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 8.0, "C": 3.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263248</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 5.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263312</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 15.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263377</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263442</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>{"A": 23.0, "B": 2.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263506</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 1.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263570</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 5.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263634</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 5.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263698</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 5.0, "C": 4.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263762</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>5</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 3.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263827</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>5</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 0.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263891</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>{"A": 22.0, "B": 2.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.263956</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 18.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 15.0, "C": 4.0, "D": 6.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264093</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264158</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>5</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 14.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264223</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>5</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 2.0, "C": 9.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264288</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264352</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 0.0, "C": 3.0, "D": 7.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264437</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 22.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264515</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>5</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 1.0, "C": 13.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264580</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 17.0, "C": 2.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264646</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 3.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264710</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 9.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264775</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264840</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>{"A": 10.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264906</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 16.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.264970</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 15.0, "C": 0.0, "D": 10.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265041</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>5</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 6.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265108</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 6.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265174</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>5</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 7.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265235</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>5</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 11.0, "C": 3.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265295</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 3.0, "C": 13.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265355</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 4.0, "C": 1.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265414</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265472</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 19.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265531</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 7.0, "C": 18.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265589</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 4.0, "C": 22.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265648</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265706</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 0.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265766</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 11.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265824</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>5</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 5.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265883</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>5</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 16.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.265941</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>5</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 6.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266000</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>5</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 2.0, "C": 4.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266062</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>5</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266129</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>5</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 5.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266193</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>5</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 0.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266257</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>5</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 2.0, "C": 4.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266322</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>5</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 1.0, "C": 9.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266387</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>5</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266452</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>5</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>{"A": 20.0, "B": 0.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266516</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>5</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 14.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266581</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>5</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 13.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266647</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>5</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 0.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266711</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>5</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266776</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>5</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>{"A": 14.0, "B": 3.0, "C": 3.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266841</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 1.0, "C": 14.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266906</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>5</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 0.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.266971</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>5</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 19.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267038</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>5</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 1.0, "C": 15.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267103</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>5</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 18.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267169</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>5</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 1.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267227</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>5</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 12.0, "C": 6.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267295</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>5</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267356</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>5</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 3.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267416</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>5</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 2.0, "C": 18.0, "D": 2.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267475</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 13.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267534</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>5</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 1.0, "C": 5.0, "D": 18.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267593</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>5</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267651</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>5</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267710</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>5</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 15.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267768</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>5</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 4.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267826</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>5</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 2.0, "C": 1.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267885</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>5</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 2.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.267943</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>5</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 20.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268002</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>5</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 0.0, "C": 17.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268074</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268140</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>5</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>{"A": 16.0, "B": 3.0, "C": 0.0, "D": 5.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268202</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>5</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 19.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268260</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>5</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>{"A": 0.0, "B": 14.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268318</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>5</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>{"A": 26.0, "B": 3.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268377</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>5</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268435</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>5</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 5.0, "C": 24.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268493</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>5</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>{"A": 29.0, "B": 1.0, "C": 2.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268552</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>5</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 2.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268611</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>5</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>{"A": 24.0, "B": 9.0, "C": 0.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268669</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>5</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 2.0, "C": 8.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268728</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>5</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>{"A": 7.0, "B": 3.0, "C": 12.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268787</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>5</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 4.0, "C": 11.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268846</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>5</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 2.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268906</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>5</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>{"A": 28.0, "B": 2.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.268971</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>5</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 16.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269041</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>5</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 20.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269107</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>5</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 3.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269166</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>5</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 17.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269225</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>5</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>{"A": 17.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269290</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 3.0, "C": 22.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269355</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>5</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 3.0, "C": 3.0, "D": 12.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269420</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>5</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 23.0, "C": 6.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269485</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>5</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>{"A": 13.0, "B": 4.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269553</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>5</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 21.0, "C": 3.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269618</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>5</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 3.0, "C": 1.0, "D": 28.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269683</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>5</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>{"A": 5.0, "B": 18.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269748</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>5</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269813</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>5</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 11.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269880</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>5</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 2.0, "C": 21.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.269945</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>5</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 16.0, "C": 2.0, "D": 13.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270010</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>5</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 7.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270079</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>5</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 8.0, "C": 13.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270143</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>5</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>{"A": 9.0, "B": 7.0, "C": 9.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270202</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>5</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 24.0, "C": 2.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270260</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>5</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>{"A": 15.0, "B": 3.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270319</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>5</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>{"A": 4.0, "B": 3.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270378</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>5</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270443</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>5</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>{"A": 6.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270509</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>5</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 4.0, "C": 22.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270573</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>{"A": 2.0, "B": 12.0, "C": 15.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270638</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>5</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>{"A": 11.0, "B": 10.0, "C": 1.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270704</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>5</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>{"A": 8.0, "B": 0.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:09:24.270769</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -469,18 +469,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.597755</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.597834</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -517,18 +517,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 0.7440000000000001, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.597898</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -541,18 +541,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.597961</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -565,18 +565,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598028</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598092</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -613,18 +613,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 0.48700000000000004, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598154</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -637,18 +637,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598215</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -661,18 +661,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 0.718, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598277</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -685,18 +685,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598338</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -709,18 +709,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598400</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -733,18 +733,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598467</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -757,18 +757,18 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598530</t>
+          <t>2026-03-10T16:13:02.493781</t>
         </is>
       </c>
     </row>
@@ -781,18 +781,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598591</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -805,18 +805,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598653</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -829,18 +829,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598714</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -853,18 +853,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598775</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -877,18 +877,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598835</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -901,18 +901,18 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598896</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -925,18 +925,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 0.821, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.598956</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -949,18 +949,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 0.769, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599016</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -973,18 +973,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 12.8, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599093</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -997,18 +997,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599160</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1021,18 +1021,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 0.308, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599226</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1045,18 +1045,18 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599293</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1069,18 +1069,18 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599361</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1093,18 +1093,18 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599421</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1117,18 +1117,18 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599482</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1141,18 +1141,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599542</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1165,18 +1165,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599603</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1189,18 +1189,18 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599663</t>
+          <t>2026-03-10T16:13:02.494781</t>
         </is>
       </c>
     </row>
@@ -1213,18 +1213,18 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599723</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1237,18 +1237,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 43.6, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"5": "2C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599785</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1261,18 +1261,18 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "22992624-1", "7": "ALONSO JES\u00daS HERN\u00c1NDEZ AVENDA\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599847</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1285,18 +1285,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23075725-9", "7": "CARLOS ALBERTO NAVARRO NAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599909</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1309,18 +1309,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23083703-1", "7": "DANTE FABI\u00c1N ULLOA MOLINA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.599970</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1333,18 +1333,18 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23226019-K", "7": "ELMO ANDR\u00c9S MART\u00cdNEZ MERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600033</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1357,18 +1357,18 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "22305094-8", "7": "FABRICIANO ANTONIO CATAL\u00c1N HUEICHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600094</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1381,18 +1381,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23243196-2", "7": "FANNY LORETO COFR\u00c9 RIVAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600155</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1405,18 +1405,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 19, "Omitidas": 1, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23264208-4", "7": "FELIPE ALFREDO BRAVO CONCHA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600215</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1429,18 +1429,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 0.7440000000000001, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23098425-5", "7": "FLORENCIA EMILIA HIRIART PULGAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600275</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1453,18 +1453,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23311809-5", "7": "FRANCISCO ENRIQUE VILLARROEL FIGUEROA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600336</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1477,18 +1477,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23142034-7", "7": "GABRIEL ARTURO CHEUQUEFILO NAUTULPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600398</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1501,18 +1501,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 0.282, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23283378-5", "7": "GUILLERMO ANDR\u00c9S SOLER CANIUCURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600458</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1525,18 +1525,18 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23190323-2", "7": "ISIDORA P\u00c9REZ OYARZ\u00daN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600520</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1549,18 +1549,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 0.385, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23254686-7", "7": "JAIME RUB\u00c9N VERA NEIHUAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600580</t>
+          <t>2026-03-10T16:13:02.495782</t>
         </is>
       </c>
     </row>
@@ -1573,18 +1573,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 20, "Omitidas": 1, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 0.795, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23303825-3", "7": "JOHANN FRANCISCO BENAVENTE JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600641</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1597,18 +1597,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 0.308, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23291819-5", "7": "JONATHAN F\u00c9LIX ACU\u00d1A MARIQUEO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600701</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1621,18 +1621,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 0.41, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "22747563-3", "7": "JOSSINH SIM\u00d3N VALDEBENITO RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23096759-8", "7": "AIDETH ANAHIS ASTETE OBREQUE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600762</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1645,18 +1645,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23279870-K", "7": "LUCIANO ALBERTO DELGADO AYELEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23068616-5", "7": "ALONSO RAFAEL RODR\u00cdGUEZ AILLAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600823</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1669,18 +1669,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 0.48700000000000004, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23124964-8", "7": "PAOLO ELIAN CARRASCO GUAJARDO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23078035-8", "7": "ANGELICA ULLOA AGUAYO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600884</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1693,18 +1693,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 64.1, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 0.48700000000000004, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23335577-1", "7": "RICARDO JEREM\u00cdAS ANTONIO LICANCURA SALAZAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23367834-1", "7": "ANTONELLA ALEJANDRA CATRILAF RAIN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.600945</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1717,18 +1717,18 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{"Buenas": 32, "Malas": 7, "Omitidas": 0, "Rend": 82.1, "SIMCE": 326, "Nota": 5.7, "Logro": "Adecuado", "Puntaje": 32}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23084146-2", "7": "SAMUEL ISMAEL INZUNZA CARTES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23194865-1", "7": "ARACELLY DE LOS ANGELES CAYUFILO LEFIPAN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601006</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1741,18 +1741,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 76.9, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23078776-K", "7": "VALENTINA IGNACIA VALENZUELA ESPARZA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23195825-8", "7": "BERNARDO AN\u00cdBAL RAINAHUEL CALLICUL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601075</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1765,18 +1765,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 0.33299999999999996, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23165216-7", "7": "VALENTINA JAVIERA LLANQUIM\u00c1N ANTILLANCA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23278997-2", "7": "DANIEL ALEXIS PE\u00d1A QUEUPUMIL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601143</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1789,18 +1789,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23178287-7", "7": "VICTORIA FLORENCIA CORT\u00c9S BETANCOURT", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23095273-6", "7": "DENISE ALINE CAMPOS BELTR\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601206</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1813,18 +1813,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"5": "2A", "6": "23154617-0", "7": "YOAN PUNOY", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23266472-K", "7": "EMILIA VIANNEY ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601266</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1837,18 +1837,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23092093-1", "7": "AARON ANTONIO RAIN MILLA\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23187256-6", "7": "ESPERANZA GALATAIA ANAHI CARTER CLAVIJO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601327</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1861,18 +1861,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 30, "Malas": 9, "Omitidas": 0, "Rend": 0.769, "SIMCE": 314, "Nota": 5.3, "Logro": "Adecuado", "Puntaje": 30}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23264494-K", "7": "ANAHI ANTONIA ESPARZA \u00c1LVAREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23114253-3", "7": "FABI\u00c1N ESTEBAN ERICES REINUN", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601388</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1885,18 +1885,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 24, "Malas": 14, "Omitidas": 1, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23332401-9", "7": "BEL\u00c9N JES\u00daS HUEITRA MATAMALA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23243775-8", "7": "FELIPE IGNACIO GODOY ROJAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601448</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1909,18 +1909,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23307747-K", "7": "BENJAM\u00cdN EDUARDO ACU\u00d1A CURINAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23164005-3", "7": "FELIPE RICARDO CATRILEO PAILLALEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601509</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1933,18 +1933,18 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23248663-5", "7": "CAMILA ANTONIA PUNULAF QUISULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23349462-3", "7": "FERNANDA VALESCA LUZ BRICE\u00d1O CALFUNAO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601569</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1957,18 +1957,18 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23090987-3", "7": "CAMILO IGNACIO CASANOVA CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23015302-7", "7": "FRANCISCO ALEXANDER GARC\u00c9S RIVERA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601629</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -1981,18 +1981,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23096566-8", "7": "CARLOS MAT\u00cdAS PINILLA BRAVO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23964755-3", "7": "FRANCO EZEQUIEL ZARATE ROLD\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601690</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2005,18 +2005,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 0.308, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23136835-3", "7": "GIOHANS EDUARDO \u00d1ANCO HUILIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "22530419-K", "7": "GIOVANNY IGNACIO SAN MART\u00cdN PATI\u00d1O", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601750</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2029,18 +2029,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 15, "Malas": 18, "Omitidas": 6, "Rend": 0.385, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23307109-9", "7": "HENRY ARIEL KUTSCHER RAM\u00cdREZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23077073-5", "7": "H\u00c9CTOR ALEXIS VILLARROEL CONTRERAS", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601811</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2053,18 +2053,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23129271-3", "7": "JAIME ALBERTO DELGADO MONCADA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23195665-4", "7": "IGNACIO ALEJANDRO MONS\u00c1LVEZ RAM\u00d3N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601871</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2077,18 +2077,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23364347-5", "7": "JOAQU\u00cdN IGNACIO MU\u00d1OZ GU\u00cd\u00d1EZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23121281-7", "7": "JAVIERA JASM\u00cdN MARIFILO EPU\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601932</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2101,18 +2101,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 0.462, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23254876-2", "7": "JOAQU\u00cdN ISAAC VEL\u00c1SQUEZ WEVAR", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23237047-5", "7": "LUIS ALBERTO NAVARRETE COFR\u00c9", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.601993</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2125,18 +2125,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 5, "Malas": 28, "Omitidas": 6, "Rend": 0.128, "SIMCE": 177, "Nota": 1.6, "Logro": "Insuficiente", "Puntaje": 5}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23170240-7", "7": "LUIS FELIPE SOBARZO MORALES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23026868-1", "7": "LUIS MARIO LEFICHE HUICHULEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602060</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2149,18 +2149,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 19, "Omitidas": 2, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 21, "Malas": 17, "Omitidas": 1, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23138672-6", "7": "MAGDALENA FRANSHESCA MU\u00d1OZ ALTAMIRANO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23003429-K", "7": "MARCELA ALEJANDRA CUR\u00cdN MONSALVE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602129</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2173,18 +2173,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23163042-2", "7": "MART\u00cdN ALEXIS CARIMAN CURI\u00d1ANCO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23225723-7", "7": "MARITZA ANDREA BELLO HUEITRA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602194</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2197,18 +2197,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "22583629-9", "7": "MART\u00cdN ALONSO CALDER\u00d3N MARILEF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23131840-2", "7": "MART\u00cdN FELIPE REINAHUEL MONTENEGRO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602254</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2221,18 +2221,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23156392-K", "7": "MAT\u00cdAS CRISTOPHER OVANDO LEIVA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23076604-5", "7": "MARTINA ANTONELLA B\u00d3RQUEZ MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602315</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2245,18 +2245,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 20, "Malas": 18, "Omitidas": 1, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23280628-1", "7": "MAXIMILIANO ANTONIO ARIAS SANDOVAL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23276851-7", "7": "MARTINA ROC\u00cdO LE\u00d3N GONZ\u00c1LEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602375</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2269,18 +2269,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{"Buenas": 18, "Malas": 21, "Omitidas": 0, "Rend": 46.2, "SIMCE": 248, "Nota": 3.3, "Logro": "Elemental", "Puntaje": 18}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23248366-0", "7": "NATACHA ANDREA PUNOI NAVARRETE", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23138775-7", "7": "MAT\u00cdAS ANDR\u00c9S RAM\u00d3N MU\u00d1OZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602436</t>
+          <t>2026-03-10T16:13:02.496782</t>
         </is>
       </c>
     </row>
@@ -2293,18 +2293,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{"Buenas": 11, "Malas": 19, "Omitidas": 9, "Rend": 28.2, "SIMCE": 210, "Nota": 2.4, "Logro": "Insuficiente", "Puntaje": 11}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23146205-8", "7": "PATRICIA MARIELA CATRILAF ANTIP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "20338382-7", "7": "MAXIMO RAIMUNDO PA\u00d1IAN JARAMILLO", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602498</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2317,18 +2317,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23307151-K", "7": "VALERIE ARACELI HERRERA OLIVARES", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23366739-0", "7": "MELIXA ALEJANDRA LEFINAO LLANCAP\u00c1N", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602565</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2341,18 +2341,18 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{"Buenas": 15, "Malas": 24, "Omitidas": 0, "Rend": 38.5, "SIMCE": 232, "Nota": 2.9, "Logro": "Insuficiente", "Puntaje": 15}</t>
+          <t>{"Buenas": 25, "Malas": 14, "Omitidas": 0, "Rend": 0.6409999999999999, "SIMCE": 287, "Nota": 4.3, "Logro": "Elemental", "Puntaje": 25}</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23356599-7", "7": "VICENTE ALEJANDRO AGUILERA CH\u00c1VEZ", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23298489-9", "7": "RENATO FRANCISCO CANIULEF CATRICURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602662</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2365,18 +2365,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{"Buenas": 31, "Malas": 8, "Omitidas": 0, "Rend": 79.5, "SIMCE": 320, "Nota": 5.5, "Logro": "Adecuado", "Puntaje": 31}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 0.48700000000000004, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23126266-0", "7": "V\u00cdCTOR HUGO MAZA REINAHUEL", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23332611-9", "7": "RICARDO ARTURO CHOCORI CHOCORI", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602743</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2389,18 +2389,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 17, "Malas": 22, "Omitidas": 0, "Rend": 0.436, "SIMCE": 243, "Nota": 3.2, "Logro": "Elemental", "Puntaje": 17}</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"5": "2B", "6": "23295647-K", "7": "YASMIN ANA\u00cdS AILLAP\u00c1N CATRILAF", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
+          <t>{"5": "2C", "6": "23203396-7", "7": "SEBASTIAN MILLACURA", "8": "Lenguaje", "9": "Noviembre", "10": "5", "4": "2025"}</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602812</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 25.6, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
+          <t>{"Buenas": 10, "Malas": 28, "Omitidas": 1, "Rend": 0.256, "SIMCE": 204, "Nota": 2.3, "Logro": "Insuficiente", "Puntaje": 10}</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2424,7 +2424,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602880</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2448,7 +2448,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.602947</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2472,7 +2472,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603014</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2496,7 +2496,7 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603091</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 0.41, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2520,7 +2520,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603159</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603225</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 35.9, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
+          <t>{"Buenas": 14, "Malas": 25, "Omitidas": 0, "Rend": 0.359, "SIMCE": 226, "Nota": 2.8, "Logro": "Insuficiente", "Puntaje": 14}</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2568,7 +2568,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603286</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 71.8, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
+          <t>{"Buenas": 28, "Malas": 11, "Omitidas": 0, "Rend": 0.718, "SIMCE": 303, "Nota": 4.9, "Logro": "Adecuado", "Puntaje": 28}</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2592,7 +2592,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603348</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 30.8, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
+          <t>{"Buenas": 12, "Malas": 27, "Omitidas": 0, "Rend": 0.308, "SIMCE": 215, "Nota": 2.5, "Logro": "Insuficiente", "Puntaje": 12}</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603409</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2640,7 +2640,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603470</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2664,7 +2664,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603532</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2688,7 +2688,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603593</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 66.7, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
+          <t>{"Buenas": 26, "Malas": 13, "Omitidas": 0, "Rend": 0.667, "SIMCE": 292, "Nota": 4.5, "Logro": "Adecuado", "Puntaje": 26}</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2712,7 +2712,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603656</t>
+          <t>2026-03-10T16:13:02.498285</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 27, "Malas": 11, "Omitidas": 1, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2736,7 +2736,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603723</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 48.7, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
+          <t>{"Buenas": 19, "Malas": 20, "Omitidas": 0, "Rend": 0.48700000000000004, "SIMCE": 254, "Nota": 3.4, "Logro": "Elemental", "Puntaje": 19}</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603804</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 59.0, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
+          <t>{"Buenas": 23, "Malas": 16, "Omitidas": 0, "Rend": 0.59, "SIMCE": 276, "Nota": 4.0, "Logro": "Elemental", "Puntaje": 23}</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2784,7 +2784,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.603900</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2808,7 +2808,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604002</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 53.8, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
+          <t>{"Buenas": 21, "Malas": 18, "Omitidas": 0, "Rend": 0.5379999999999999, "SIMCE": 265, "Nota": 3.7, "Logro": "Elemental", "Puntaje": 21}</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2832,7 +2832,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604096</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 33.3, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
+          <t>{"Buenas": 13, "Malas": 26, "Omitidas": 0, "Rend": 0.33299999999999996, "SIMCE": 221, "Nota": 2.7, "Logro": "Insuficiente", "Puntaje": 13}</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2856,7 +2856,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604168</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2880,7 +2880,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604237</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 51.3, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
+          <t>{"Buenas": 20, "Malas": 19, "Omitidas": 0, "Rend": 0.513, "SIMCE": 259, "Nota": 3.6, "Logro": "Elemental", "Puntaje": 20}</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604305</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 74.4, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
+          <t>{"Buenas": 29, "Malas": 10, "Omitidas": 0, "Rend": 0.7440000000000001, "SIMCE": 309, "Nota": 5.1, "Logro": "Adecuado", "Puntaje": 29}</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2928,7 +2928,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604367</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 41.0, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
+          <t>{"Buenas": 16, "Malas": 23, "Omitidas": 0, "Rend": 0.41, "SIMCE": 237, "Nota": 3.1, "Logro": "Insuficiente", "Puntaje": 16}</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2952,7 +2952,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604429</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 61.5, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
+          <t>{"Buenas": 24, "Malas": 15, "Omitidas": 0, "Rend": 0.615, "SIMCE": 281, "Nota": 4.1, "Logro": "Elemental", "Puntaje": 24}</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2976,7 +2976,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604503</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 56.4, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
+          <t>{"Buenas": 22, "Malas": 17, "Omitidas": 0, "Rend": 0.564, "SIMCE": 270, "Nota": 3.8, "Logro": "Elemental", "Puntaje": 22}</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3000,7 +3000,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604601</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 69.2, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
+          <t>{"Buenas": 27, "Malas": 12, "Omitidas": 0, "Rend": 0.6920000000000001, "SIMCE": 298, "Nota": 4.7, "Logro": "Adecuado", "Puntaje": 27}</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3024,7 +3024,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:23.604685</t>
+          <t>2026-03-10T16:13:02.499288</t>
         </is>
       </c>
     </row>
@@ -3037,18 +3037,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 11.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260577</t>
+          <t>2026-03-10T16:13:02.613559</t>
         </is>
       </c>
     </row>
@@ -3061,18 +3061,18 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{"A": 20.0, "B": 2.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 16.0, "B": 5.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a", "Rend": 0.6956521739130435}</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260659</t>
+          <t>2026-03-10T16:13:02.613559</t>
         </is>
       </c>
     </row>
@@ -3085,18 +3085,18 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 15.0, "C": 0.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 5.0, "B": 16.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "b", "Rend": 0.6956521739130435}</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260728</t>
+          <t>2026-03-10T16:13:02.613559</t>
         </is>
       </c>
     </row>
@@ -3109,18 +3109,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 3.0, "C": 19.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 6.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260795</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3133,18 +3133,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{"A": 18.0, "B": 4.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 16.0, "B": 2.0, "C": 4.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260864</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3157,18 +3157,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 0.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 20.0, "E": 0.0, "Correcta": "d", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260930</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3181,18 +3181,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{"A": 15.0, "B": 6.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 16.0, "B": 5.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.20833333333333334}</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.260995</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3205,18 +3205,18 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{"A": 9.0, "B": 0.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 5.0, "B": 0.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.7083333333333334}</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261083</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3229,18 +3229,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 6.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 5.0, "B": 2.0, "C": 4.0, "D": 13.0, "E": 0.0, "Correcta": "d", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261151</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3253,18 +3253,18 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 6.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 2.0, "B": 1.0, "C": 9.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261216</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3277,18 +3277,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{"A": 9.0, "B": 0.0, "C": 10.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 8.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "c", "Rend": 0.4166666666666667}</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261282</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3301,18 +3301,18 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{"A": 18.0, "B": 1.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 20.0, "B": 0.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261348</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3325,18 +3325,18 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 11.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 14.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261413</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3349,18 +3349,18 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 15.0, "C": 5.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 3.0, "B": 13.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261478</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3373,18 +3373,18 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 3.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 2.0, "B": 0.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261544</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3397,18 +3397,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 15.0, "C": 4.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 7.0, "E": 0.0, "Correcta": "c", "Rend": 0.25}</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261609</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3421,18 +3421,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{"A": 12.0, "B": 2.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 14.0, "B": 3.0, "C": 3.0, "D": 4.0, "E": 0.0, "Correcta": "a", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261674</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3445,18 +3445,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 1.0, "C": 15.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 6.0, "B": 1.0, "C": 14.0, "D": 3.0, "E": 0.0, "Correcta": "c", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261739</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3469,18 +3469,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 0.0, "C": 0.0, "D": 13.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 13.0, "B": 0.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "a", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261804</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3493,18 +3493,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 16.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 0.0, "B": 19.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.7916666666666666}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261869</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3517,18 +3517,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 0.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 7.0, "B": 1.0, "C": 15.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261934</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3541,18 +3541,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 13.0, "C": 3.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 18.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b", "Rend": 0.75}</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.261999</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3565,18 +3565,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 5.0, "C": 3.0, "D": 16.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 0.0, "C": 1.0, "D": 23.0, "E": 0.0, "Correcta": "d", "Rend": 0.9583333333333334}</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262071</t>
+          <t>2026-03-10T16:13:02.614559</t>
         </is>
       </c>
     </row>
@@ -3589,18 +3589,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 10.0, "C": 7.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 4.0, "B": 12.0, "C": 6.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.16666666666666666}</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262136</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3613,18 +3613,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 9.0, "C": 3.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262201</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3637,18 +3637,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 4.0, "C": 11.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 5.0, "B": 3.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a", "Rend": 0.20833333333333334}</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262266</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3661,18 +3661,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 0.0, "C": 20.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 2.0, "C": 18.0, "D": 2.0, "E": 0.0, "Correcta": "c", "Rend": 0.75}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262330</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3685,18 +3685,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 11.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 13.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "b", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262396</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3709,18 +3709,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 1.0, "C": 5.0, "D": 18.0, "E": 0.0, "Correcta": "d", "Rend": 0.75}</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262462</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3733,18 +3733,18 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 8.0, "C": 5.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 3.0, "B": 7.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "c", "Rend": 0.4166666666666667}</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262527</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3757,18 +3757,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 4.0, "C": 4.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 8.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "d", "Rend": 0.4166666666666667}</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262592</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3781,18 +3781,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 13.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 15.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262657</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3805,18 +3805,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 1.0, "C": 5.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 11.0, "B": 4.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.4583333333333333}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262721</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3829,18 +3829,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 2.0, "C": 2.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 2.0, "C": 1.0, "D": 20.0, "E": 0.0, "Correcta": "d", "Rend": 0.8695652173913043}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262786</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3853,18 +3853,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 0.0, "E": 0.0}</t>
+          <t>{"A": 0.0, "B": 2.0, "C": 0.0, "D": 0.0, "E": 0.0, "Rend": 0.0}</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262850</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3877,18 +3877,18 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 14.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 3.0, "B": 20.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262915</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3901,18 +3901,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 0.0, "B": 0.0, "C": 17.0, "D": 7.0, "E": 0.0, "Correcta": "c", "Rend": 0.7083333333333334}</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.262980</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3925,18 +3925,18 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 4.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 1.0, "E": 0.0, "Correcta": "b", "Rend": 0.4166666666666667}</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263052</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3949,18 +3949,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 7.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 16.0, "B": 3.0, "C": 0.0, "D": 5.0, "E": 0.0, "Correcta": "a", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263118</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3973,18 +3973,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 0.0, "C": 7.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 19.0, "E": 0.0, "Correcta": "d", "Rend": 0.7916666666666666}</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263183</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -3997,18 +3997,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 8.0, "C": 3.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263248</t>
+          <t>2026-03-10T16:13:02.615559</t>
         </is>
       </c>
     </row>
@@ -4021,18 +4021,18 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{"A": 20.0, "B": 5.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 20.0, "B": 2.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263312</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4045,18 +4045,18 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 15.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 15.0, "C": 0.0, "D": 7.0, "E": 0.0, "Correcta": "b", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263377</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4069,18 +4069,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 3.0, "C": 19.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.7916666666666666}</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263442</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4093,18 +4093,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{"A": 23.0, "B": 2.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 18.0, "B": 4.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a", "Rend": 0.75}</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263506</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4117,18 +4117,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 1.0, "C": 1.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 8.0, "B": 0.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263570</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4141,18 +4141,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{"A": 20.0, "B": 5.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 15.0, "B": 6.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.25}</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263634</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4165,18 +4165,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 1.0, "C": 5.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 9.0, "B": 0.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "d", "Rend": 0.5833333333333334}</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263698</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4189,18 +4189,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 5.0, "C": 4.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 8.0, "B": 6.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "d", "Rend": 0.375}</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263762</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4213,18 +4213,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{"A": 9.0, "B": 3.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 6.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "d", "Rend": 0.375}</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263827</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4237,18 +4237,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 0.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 9.0, "B": 0.0, "C": 10.0, "D": 5.0, "E": 0.0, "Correcta": "c", "Rend": 0.4166666666666667}</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263891</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4261,18 +4261,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{"A": 22.0, "B": 2.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 18.0, "B": 1.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.75}</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.263956</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4285,18 +4285,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 18.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 11.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "b", "Rend": 0.4583333333333333}</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264026</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4309,18 +4309,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 15.0, "C": 4.0, "D": 6.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 15.0, "C": 5.0, "D": 2.0, "E": 0.0, "Correcta": "b", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264093</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4333,18 +4333,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 0.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 3.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.7083333333333334}</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264158</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4357,18 +4357,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 14.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 0.0, "B": 15.0, "C": 4.0, "D": 5.0, "E": 0.0, "Correcta": "c", "Rend": 0.16666666666666666}</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264223</t>
+          <t>2026-03-10T16:13:02.616560</t>
         </is>
       </c>
     </row>
@@ -4381,18 +4381,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 2.0, "C": 9.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 12.0, "B": 2.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "a", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264288</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4405,18 +4405,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 2.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 4.0, "B": 1.0, "C": 15.0, "D": 4.0, "E": 0.0, "Correcta": "c", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264352</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4429,18 +4429,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 0.0, "C": 3.0, "D": 7.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 11.0, "B": 0.0, "C": 0.0, "D": 13.0, "E": 0.0, "Correcta": "a", "Rend": 0.4583333333333333}</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264437</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4453,18 +4453,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 22.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 3.0, "B": 16.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264515</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4477,18 +4477,18 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 1.0, "C": 13.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 8.0, "B": 0.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264580</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4501,18 +4501,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 17.0, "C": 2.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 0.0, "B": 13.0, "C": 3.0, "D": 8.0, "E": 0.0, "Correcta": "b", "Rend": 0.5416666666666666}</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264646</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4525,18 +4525,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 3.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 5.0, "C": 3.0, "D": 16.0, "E": 0.0, "Correcta": "d", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264710</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4549,18 +4549,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 9.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 6.0, "B": 10.0, "C": 7.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.25}</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264775</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4573,18 +4573,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 7.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 1.0, "B": 9.0, "C": 3.0, "D": 11.0, "E": 0.0, "Correcta": "d", "Rend": 0.4583333333333333}</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264840</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4597,18 +4597,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{"A": 10.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 8.0, "B": 4.0, "C": 11.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.3333333333333333}</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264906</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4621,18 +4621,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 2.0, "C": 16.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 3.0, "B": 0.0, "C": 20.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.8333333333333334}</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.264970</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4645,18 +4645,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 15.0, "C": 0.0, "D": 10.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 11.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "b", "Rend": 0.4583333333333333}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265041</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4669,18 +4669,18 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 6.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265108</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4693,18 +4693,18 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 6.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 5.0, "B": 8.0, "C": 5.0, "D": 6.0, "E": 0.0, "Correcta": "c", "Rend": 0.20833333333333334}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265174</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4717,18 +4717,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 7.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 4.0, "C": 4.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.5217391304347826}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265235</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4741,18 +4741,18 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{"A": 9.0, "B": 11.0, "C": 3.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 13.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b", "Rend": 0.5652173913043478}</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265295</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4765,18 +4765,18 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 3.0, "C": 13.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 16.0, "B": 1.0, "C": 5.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.6956521739130435}</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265355</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4789,18 +4789,18 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 4.0, "C": 1.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 2.0, "C": 2.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.5217391304347826}</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265414</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4813,18 +4813,18 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 0.0, "E": 0.0, "Rend": 0.0}</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265472</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4837,18 +4837,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 19.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 8.0, "B": 14.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.6086956521739131}</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265531</t>
+          <t>2026-03-10T16:13:02.617559</t>
         </is>
       </c>
     </row>
@@ -4861,18 +4861,18 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 7.0, "C": 18.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.5217391304347826}</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265589</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -4885,18 +4885,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 4.0, "C": 22.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 4.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "b", "Rend": 0.17391304347826086}</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265648</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -4909,18 +4909,18 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 5.0, "B": 7.0, "C": 1.0, "D": 9.0, "E": 0.0, "Correcta": "a", "Rend": 0.22727272727272727}</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265706</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -4933,18 +4933,18 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{"A": 13.0, "B": 0.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 0.0, "C": 7.0, "D": 8.0, "E": 0.0, "Correcta": "d", "Rend": 0.36363636363636365}</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2B", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265766</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -4957,18 +4957,18 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 11.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 14.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.5151515151515151}</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265824</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -4981,18 +4981,18 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 5.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 26.0, "B": 3.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.7878787878787878}</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265883</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5005,18 +5005,18 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 16.0, "C": 0.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 7.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.265941</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5029,18 +5029,18 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 6.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 3.0, "B": 5.0, "C": 24.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.7272727272727273}</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266000</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5053,18 +5053,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 2.0, "C": 4.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 29.0, "B": 1.0, "C": 2.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.8787878787878788}</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266062</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5077,18 +5077,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 4.0, "B": 2.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d", "Rend": 0.71875}</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266129</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5101,18 +5101,18 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 5.0, "C": 3.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 24.0, "B": 9.0, "C": 0.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.2727272727272727}</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266193</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5125,18 +5125,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 0.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 6.0, "B": 2.0, "C": 8.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.5151515151515151}</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266257</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5149,18 +5149,18 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 2.0, "C": 4.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 3.0, "C": 12.0, "D": 11.0, "E": 0.0, "Correcta": "d", "Rend": 0.3333333333333333}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266322</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5173,18 +5173,18 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 1.0, "C": 9.0, "D": 12.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 5.0, "B": 4.0, "C": 11.0, "D": 13.0, "E": 0.0, "Correcta": "d", "Rend": 0.3939393939393939}</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266387</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5197,18 +5197,18 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 13.0, "B": 2.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "c", "Rend": 0.3333333333333333}</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266452</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5221,18 +5221,18 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{"A": 20.0, "B": 0.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 28.0, "B": 2.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.875}</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266516</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5245,18 +5245,18 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 14.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 8.0, "B": 16.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266581</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5269,18 +5269,18 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 13.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 20.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b", "Rend": 0.625}</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266647</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5293,18 +5293,18 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 0.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 4.0, "B": 3.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d", "Rend": 0.7272727272727273}</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266711</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5317,18 +5317,18 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 6.0, "B": 17.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c", "Rend": 0.15151515151515152}</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266776</t>
+          <t>2026-03-10T16:13:02.618673</t>
         </is>
       </c>
     </row>
@@ -5341,18 +5341,18 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{"A": 14.0, "B": 3.0, "C": 3.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 17.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "a", "Rend": 0.5151515151515151}</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266841</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5365,18 +5365,18 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 1.0, "C": 14.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 3.0, "B": 3.0, "C": 22.0, "D": 5.0, "E": 0.0, "Correcta": "c", "Rend": 0.6666666666666666}</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266906</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5389,18 +5389,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{"A": 13.0, "B": 0.0, "C": 2.0, "D": 9.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 15.0, "B": 3.0, "C": 3.0, "D": 12.0, "E": 0.0, "Correcta": "a", "Rend": 0.45454545454545453}</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.266971</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5413,18 +5413,18 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 19.0, "C": 5.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 23.0, "C": 6.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.696969696969697}</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267038</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5437,18 +5437,18 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 1.0, "C": 15.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 13.0, "B": 4.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.48484848484848486}</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267103</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5461,18 +5461,18 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 18.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 4.0, "B": 21.0, "C": 3.0, "D": 5.0, "E": 0.0, "Correcta": "b", "Rend": 0.6363636363636364}</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267169</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5485,18 +5485,18 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 0.0, "C": 1.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 1.0, "B": 3.0, "C": 1.0, "D": 28.0, "E": 0.0, "Correcta": "d", "Rend": 0.8484848484848485}</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267227</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5509,18 +5509,18 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 12.0, "C": 6.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 5.0, "B": 18.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.15151515151515152}</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INFERIR"}</t>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267295</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5533,18 +5533,18 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 7.0, "C": 3.0, "D": 14.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 15.0, "E": 0.0, "Correcta": "d", "Rend": 0.46875}</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267356</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5557,18 +5557,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 3.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 8.0, "B": 11.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "a", "Rend": 0.24242424242424243}</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267416</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5581,18 +5581,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 2.0, "C": 18.0, "D": 2.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 6.0, "B": 2.0, "C": 21.0, "D": 4.0, "E": 0.0, "Correcta": "c", "Rend": 0.6363636363636364}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267475</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5605,18 +5605,18 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 13.0, "C": 2.0, "D": 8.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 16.0, "C": 2.0, "D": 13.0, "E": 0.0, "Correcta": "b", "Rend": 0.48484848484848486}</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267534</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5629,18 +5629,18 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 1.0, "C": 5.0, "D": 18.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 7.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d", "Rend": 0.6363636363636364}</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267593</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5653,18 +5653,18 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 7.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 6.0, "B": 8.0, "C": 13.0, "D": 6.0, "E": 0.0, "Correcta": "c", "Rend": 0.3939393939393939}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267651</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5677,18 +5677,18 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 9.0, "B": 7.0, "C": 9.0, "D": 8.0, "E": 0.0, "Correcta": "d", "Rend": 0.24242424242424243}</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267710</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5701,18 +5701,18 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 15.0, "C": 2.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 3.0, "B": 24.0, "C": 2.0, "D": 4.0, "E": 0.0, "Correcta": "b", "Rend": 0.7272727272727273}</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267768</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5725,18 +5725,18 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 4.0, "C": 7.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 15.0, "B": 3.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "a", "Rend": 0.45454545454545453}</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267826</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5749,18 +5749,18 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 2.0, "C": 1.0, "D": 20.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 4.0, "B": 3.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d", "Rend": 0.696969696969697}</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267885</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5773,18 +5773,18 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 2.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0, "Rend": 0.0}</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.267943</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5797,18 +5797,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 20.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 6.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b", "Rend": 0.6875}</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "SINTETIZAR"}</t>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268002</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5821,18 +5821,18 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 0.0, "C": 17.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 4.0, "C": 22.0, "D": 3.0, "E": 0.0, "Correcta": "c", "Rend": 0.7096774193548387}</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "INTERPRETAR"}</t>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268074</t>
+          <t>2026-03-10T16:13:02.619671</t>
         </is>
       </c>
     </row>
@@ -5845,18 +5845,18 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 10.0, "C": 12.0, "D": 1.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 12.0, "C": 15.0, "D": 2.0, "E": 0.0, "Correcta": "b", "Rend": 0.3870967741935484}</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268140</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5869,18 +5869,18 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>{"A": 16.0, "B": 3.0, "C": 0.0, "D": 5.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 11.0, "B": 10.0, "C": 1.0, "D": 8.0, "E": 0.0, "Correcta": "a", "Rend": 0.36666666666666664}</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "EVALUAR"}</t>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268202</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5893,18 +5893,18 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 1.0, "D": 19.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 8.0, "B": 0.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d", "Rend": 0.6774193548387096}</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2A", "12": "LOCALIZAR"}</t>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268260</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5917,18 +5917,18 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>{"A": 0.0, "B": 14.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 8.0, "C": 3.0, "D": 15.0, "E": 0.0, "Correcta": "d", "Rend": 0.5769230769230769}</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "1", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268318</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5941,18 +5941,18 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>{"A": 26.0, "B": 3.0, "C": 3.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 20.0, "B": 5.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.7692307692307693}</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "2", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268377</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5965,18 +5965,18 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 5.0, "B": 15.0, "C": 1.0, "D": 5.0, "E": 0.0, "Correcta": "b", "Rend": 0.5769230769230769}</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "3", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268435</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -5989,18 +5989,18 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 5.0, "C": 24.0, "D": 1.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 3.0, "B": 1.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.8076923076923077}</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "4", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268493</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6013,18 +6013,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>{"A": 29.0, "B": 1.0, "C": 2.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 23.0, "B": 2.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "a", "Rend": 0.8846153846153846}</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "5", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268552</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6037,18 +6037,18 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 2.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 1.0, "C": 1.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.6538461538461539}</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "6", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268611</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6061,18 +6061,18 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>{"A": 24.0, "B": 9.0, "C": 0.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 20.0, "B": 5.0, "C": 1.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.19230769230769232}</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "7", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268669</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6085,18 +6085,18 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 2.0, "C": 8.0, "D": 17.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 7.0, "B": 1.0, "C": 5.0, "D": 13.0, "E": 0.0, "Correcta": "d", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "8", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268728</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6109,18 +6109,18 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>{"A": 7.0, "B": 3.0, "C": 12.0, "D": 11.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 5.0, "B": 5.0, "C": 4.0, "D": 11.0, "E": 0.0, "Correcta": "d", "Rend": 0.44}</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "9", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268787</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6133,18 +6133,18 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 4.0, "C": 11.0, "D": 13.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 9.0, "B": 3.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d", "Rend": 0.38461538461538464}</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "10", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268846</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6157,18 +6157,18 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>{"A": 13.0, "B": 2.0, "C": 11.0, "D": 7.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 11.0, "B": 0.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "c", "Rend": 0.46153846153846156}</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "11", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268906</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6181,18 +6181,18 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>{"A": 28.0, "B": 2.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 22.0, "B": 2.0, "C": 2.0, "D": 0.0, "E": 0.0, "Correcta": "a", "Rend": 0.8461538461538461}</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "12", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.268971</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6205,18 +6205,18 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 16.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 3.0, "B": 18.0, "C": 3.0, "D": 2.0, "E": 0.0, "Correcta": "b", "Rend": 0.6923076923076923}</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "13", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269041</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6229,18 +6229,18 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 20.0, "C": 4.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 15.0, "C": 4.0, "D": 6.0, "E": 0.0, "Correcta": "b", "Rend": 0.5769230769230769}</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "14", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269107</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6253,18 +6253,18 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 3.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 0.0, "B": 0.0, "C": 2.0, "D": 24.0, "E": 0.0, "Correcta": "d", "Rend": 0.9230769230769231}</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
+          <t>{"11": "15", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269166</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6277,18 +6277,18 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 17.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 14.0, "C": 5.0, "D": 5.0, "E": 0.0, "Correcta": "c", "Rend": 0.19230769230769232}</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "16", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269225</t>
+          <t>2026-03-10T16:13:02.620671</t>
         </is>
       </c>
     </row>
@@ -6301,18 +6301,18 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{"A": 17.0, "B": 3.0, "C": 3.0, "D": 10.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 11.0, "B": 2.0, "C": 9.0, "D": 4.0, "E": 0.0, "Correcta": "a", "Rend": 0.4230769230769231}</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "17", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269290</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6325,18 +6325,18 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 3.0, "C": 22.0, "D": 5.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 2.0, "C": 21.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.8076923076923077}</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "18", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269355</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6349,18 +6349,18 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>{"A": 15.0, "B": 3.0, "C": 3.0, "D": 12.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 16.0, "B": 0.0, "C": 3.0, "D": 7.0, "E": 0.0, "Correcta": "a", "Rend": 0.6153846153846154}</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "19", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269420</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6373,18 +6373,18 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 23.0, "C": 6.0, "D": 0.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 22.0, "C": 1.0, "D": 1.0, "E": 0.0, "Correcta": "b", "Rend": 0.88}</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "20", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269485</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6397,18 +6397,18 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>{"A": 13.0, "B": 4.0, "C": 16.0, "D": 0.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 11.0, "B": 1.0, "C": 13.0, "D": 1.0, "E": 0.0, "Correcta": "c", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "21", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269553</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6421,18 +6421,18 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 21.0, "C": 3.0, "D": 5.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 2.0, "B": 17.0, "C": 2.0, "D": 5.0, "E": 0.0, "Correcta": "b", "Rend": 0.6538461538461539}</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "22", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269618</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6445,18 +6445,18 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 3.0, "C": 1.0, "D": 28.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 1.0, "B": 3.0, "C": 2.0, "D": 20.0, "E": 0.0, "Correcta": "d", "Rend": 0.7692307692307693}</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "23", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269683</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6469,18 +6469,18 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>{"A": 5.0, "B": 18.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 7.0, "B": 9.0, "C": 8.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.2692307692307692}</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INFERIR"}</t>
+          <t>{"11": "24", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INFERIR"}</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269748</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6493,18 +6493,18 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>{"A": 1.0, "B": 10.0, "C": 6.0, "D": 15.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 3.0, "B": 7.0, "C": 3.0, "D": 13.0, "E": 0.0, "Correcta": "d", "Rend": 0.5}</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "25", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269813</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6517,18 +6517,18 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 11.0, "C": 10.0, "D": 4.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 10.0, "B": 0.0, "C": 10.0, "D": 6.0, "E": 0.0, "Correcta": "a", "Rend": 0.38461538461538464}</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "26", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269880</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6541,18 +6541,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 2.0, "C": 21.0, "D": 4.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 2.0, "B": 2.0, "C": 16.0, "D": 6.0, "E": 0.0, "Correcta": "c", "Rend": 0.6153846153846154}</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "27", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.269945</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6565,18 +6565,18 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 16.0, "C": 2.0, "D": 13.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 1.0, "B": 15.0, "C": 0.0, "D": 10.0, "E": 0.0, "Correcta": "b", "Rend": 0.5769230769230769}</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "28", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270010</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6589,18 +6589,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 7.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 1.0, "B": 6.0, "C": 2.0, "D": 17.0, "E": 0.0, "Correcta": "d", "Rend": 0.6538461538461539}</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "29", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270079</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6613,18 +6613,18 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 8.0, "C": 13.0, "D": 6.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 6.0, "B": 6.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "c", "Rend": 0.15384615384615385}</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "30", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270143</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6637,18 +6637,18 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>{"A": 9.0, "B": 7.0, "C": 9.0, "D": 8.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 5.0, "B": 7.0, "C": 4.0, "D": 10.0, "E": 0.0, "Correcta": "d", "Rend": 0.38461538461538464}</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "31", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270202</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6661,18 +6661,18 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 24.0, "C": 2.0, "D": 4.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 9.0, "B": 11.0, "C": 3.0, "D": 3.0, "E": 0.0, "Correcta": "b", "Rend": 0.4230769230769231}</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "32", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270260</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6685,18 +6685,18 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>{"A": 15.0, "B": 3.0, "C": 12.0, "D": 3.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 8.0, "B": 3.0, "C": 13.0, "D": 2.0, "E": 0.0, "Correcta": "a", "Rend": 0.3076923076923077}</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "33", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270319</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6709,18 +6709,18 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{"A": 4.0, "B": 3.0, "C": 3.0, "D": 23.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 6.0, "B": 4.0, "C": 1.0, "D": 15.0, "E": 0.0, "Correcta": "d", "Rend": 0.5769230769230769}</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "34", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270378</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6733,18 +6733,18 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{"A": 3.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0}</t>
+          <t>{"A": 0.0, "B": 1.0, "C": 0.0, "D": 0.0, "E": 0.0, "Rend": 0.0}</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "35", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270443</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6757,18 +6757,18 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>{"A": 6.0, "B": 22.0, "C": 1.0, "D": 3.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 6.0, "B": 19.0, "C": 0.0, "D": 1.0, "E": 0.0, "Correcta": "b", "Rend": 0.7307692307692307}</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "SINTETIZAR"}</t>
+          <t>{"11": "36", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "SINTETIZAR"}</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270509</t>
+          <t>2026-03-10T16:13:02.621671</t>
         </is>
       </c>
     </row>
@@ -6781,18 +6781,18 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 4.0, "C": 22.0, "D": 3.0, "E": 0.0, "Correcta": "c"}</t>
+          <t>{"A": 1.0, "B": 7.0, "C": 18.0, "D": 0.0, "E": 0.0, "Correcta": "c", "Rend": 0.6923076923076923}</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "INTERPRETAR"}</t>
+          <t>{"11": "37", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "INTERPRETAR"}</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270573</t>
+          <t>2026-03-10T16:13:02.622671</t>
         </is>
       </c>
     </row>
@@ -6805,18 +6805,18 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>{"A": 2.0, "B": 12.0, "C": 15.0, "D": 2.0, "E": 0.0, "Correcta": "b"}</t>
+          <t>{"A": 0.0, "B": 4.0, "C": 22.0, "D": 0.0, "E": 0.0, "Correcta": "b", "Rend": 0.15384615384615385}</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "38", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270638</t>
+          <t>2026-03-10T16:13:02.622671</t>
         </is>
       </c>
     </row>
@@ -6829,18 +6829,18 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>{"A": 11.0, "B": 10.0, "C": 1.0, "D": 8.0, "E": 0.0, "Correcta": "a"}</t>
+          <t>{"A": 4.0, "B": 7.0, "C": 1.0, "D": 14.0, "E": 0.0, "Correcta": "a", "Rend": 0.15384615384615385}</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "EVALUAR"}</t>
+          <t>{"11": "39", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "EVALUAR"}</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270704</t>
+          <t>2026-03-10T16:13:02.622671</t>
         </is>
       </c>
     </row>
@@ -6853,18 +6853,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>{"A": 8.0, "B": 0.0, "C": 2.0, "D": 21.0, "E": 0.0, "Correcta": "d"}</t>
+          <t>{"A": 13.0, "B": 0.0, "C": 1.0, "D": 12.0, "E": 0.0, "Correcta": "d", "Rend": 0.46153846153846156}</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2C", "12": "LOCALIZAR"}</t>
+          <t>{"11": "40", "4": "2025", "8": "Lenguaje", "9": "Noviembre", "10": "5", "5": "2D", "12": "LOCALIZAR"}</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-03-05T18:09:24.270769</t>
+          <t>2026-03-10T16:13:02.622671</t>
         </is>
       </c>
     </row>

--- a/data/database/metric_data.xlsx
+++ b/data/database/metric_data.xlsx
@@ -480,7 +480,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.471479</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.493781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.472982</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.474107</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.494781</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.475110</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476109</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476109</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476109</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476109</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476612</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476612</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.495782</t>
+          <t>2026-03-10T18:08:58.476612</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.476612</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.477114</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478119</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478119</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.478627</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.480142</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.496782</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.481145</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.482147</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.498285</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.483145</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.499288</t>
+          <t>2026-03-10T18:08:58.484145</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.613559</t>
+          <t>2026-03-10T18:08:59.496114</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.613559</t>
+          <t>2026-03-10T18:08:59.496114</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.613559</t>
+          <t>2026-03-10T18:08:59.496114</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.497150</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.498153</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.499154</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.499154</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.499154</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.614559</t>
+          <t>2026-03-10T18:08:59.499154</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.499656</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.500659</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.615559</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.501659</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.616560</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.502659</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.503847</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.505551</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.506557</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.617559</t>
+          <t>2026-03-10T18:08:59.506557</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.506557</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.506557</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.507059</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508064</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508064</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508064</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508568</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508568</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.508568</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.618673</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.509573</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.510577</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.510577</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.510577</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512051</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512051</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512051</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.512781</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.619671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.513785</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.514786</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.516289</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.516289</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.516289</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.517294</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.517294</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.620671</t>
+          <t>2026-03-10T18:08:59.517798</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.517798</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.517798</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.517798</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.518417</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.519448</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.519448</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.519448</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.519448</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.519448</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.520452</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.520452</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.520452</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.520452</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.521453</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.621671</t>
+          <t>2026-03-10T18:08:59.521453</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.622671</t>
+          <t>2026-03-10T18:08:59.521453</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.622671</t>
+          <t>2026-03-10T18:08:59.521453</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.622671</t>
+          <t>2026-03-10T18:08:59.521453</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-03-10T16:13:02.622671</t>
+          <t>2026-03-10T18:08:59.522452</t>
         </is>
       </c>
     </row>
